--- a/jogos_2026-01-02.xlsx
+++ b/jogos_2026-01-02.xlsx
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="M2" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="N2" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -704,10 +704,10 @@
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.9</v>
+        <v>5.8</v>
       </c>
       <c r="M14" t="n">
-        <v>3.4</v>
+        <v>4.05</v>
       </c>
       <c r="N14" t="n">
-        <v>2.4</v>
+        <v>1.58</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>5.8</v>
+        <v>2.9</v>
       </c>
       <c r="M15" t="n">
-        <v>4.05</v>
+        <v>3.4</v>
       </c>
       <c r="N15" t="n">
-        <v>1.58</v>
+        <v>2.4</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>

--- a/jogos_2026-01-02.xlsx
+++ b/jogos_2026-01-02.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.9</v>
+        <v>5.8</v>
       </c>
       <c r="M15" t="n">
-        <v>3.4</v>
+        <v>4.05</v>
       </c>
       <c r="N15" t="n">
-        <v>2.4</v>
+        <v>1.58</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>

--- a/jogos_2026-01-02.xlsx
+++ b/jogos_2026-01-02.xlsx
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>

--- a/jogos_2026-01-02.xlsx
+++ b/jogos_2026-01-02.xlsx
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>

--- a/jogos_2026-01-02.xlsx
+++ b/jogos_2026-01-02.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.9</v>
+        <v>5.8</v>
       </c>
       <c r="M15" t="n">
-        <v>3.4</v>
+        <v>4.05</v>
       </c>
       <c r="N15" t="n">
-        <v>2.4</v>
+        <v>1.58</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>

--- a/jogos_2026-01-02.xlsx
+++ b/jogos_2026-01-02.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>6.23</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1543,10 +1543,10 @@
         <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE9" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>

--- a/jogos_2026-01-02.xlsx
+++ b/jogos_2026-01-02.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>

--- a/jogos_2026-01-02.xlsx
+++ b/jogos_2026-01-02.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="M13" t="n">
-        <v>3.75</v>
+        <v>3.62</v>
       </c>
       <c r="N13" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="M16" t="n">
-        <v>4.05</v>
+        <v>3.99</v>
       </c>
       <c r="N16" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>

--- a/jogos_2026-01-02.xlsx
+++ b/jogos_2026-01-02.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>5.5</v>
+        <v>2.9</v>
       </c>
       <c r="M16" t="n">
-        <v>3.99</v>
+        <v>3.4</v>
       </c>
       <c r="N16" t="n">
-        <v>1.57</v>
+        <v>2.4</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.92</v>
+        <v>1.87</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.82</v>
+        <v>1.93</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>

--- a/jogos_2026-01-02.xlsx
+++ b/jogos_2026-01-02.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>6.23</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1424,10 +1424,10 @@
         <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE8" t="n">
         <v>0</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>6.23</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1543,10 +1543,10 @@
         <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>5.5</v>
+        <v>2.9</v>
       </c>
       <c r="M14" t="n">
-        <v>3.99</v>
+        <v>3.4</v>
       </c>
       <c r="N14" t="n">
-        <v>1.57</v>
+        <v>2.4</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.92</v>
+        <v>1.87</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.82</v>
+        <v>1.93</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.9</v>
+        <v>5.5</v>
       </c>
       <c r="M16" t="n">
-        <v>3.4</v>
+        <v>3.99</v>
       </c>
       <c r="N16" t="n">
-        <v>2.4</v>
+        <v>1.57</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.93</v>
+        <v>1.82</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>

--- a/jogos_2026-01-02.xlsx
+++ b/jogos_2026-01-02.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="M8" t="n">
-        <v>4.33</v>
+        <v>4.4</v>
       </c>
       <c r="N8" t="n">
-        <v>6.23</v>
+        <v>5.9</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1418,10 +1418,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC8" t="n">
         <v>2.38</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>5.5</v>
+        <v>2.9</v>
       </c>
       <c r="M16" t="n">
-        <v>3.99</v>
+        <v>3.4</v>
       </c>
       <c r="N16" t="n">
-        <v>1.57</v>
+        <v>2.4</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.92</v>
+        <v>1.87</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.82</v>
+        <v>1.93</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>

--- a/jogos_2026-01-02.xlsx
+++ b/jogos_2026-01-02.xlsx
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3.99</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.9</v>
+        <v>5.5</v>
       </c>
       <c r="M16" t="n">
-        <v>3.4</v>
+        <v>3.99</v>
       </c>
       <c r="N16" t="n">
-        <v>2.4</v>
+        <v>1.57</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.93</v>
+        <v>1.82</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>

--- a/jogos_2026-01-02.xlsx
+++ b/jogos_2026-01-02.xlsx
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1418,16 +1418,16 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
         <v>0</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1537,16 +1537,16 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE9" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.9</v>
+        <v>5.5</v>
       </c>
       <c r="M14" t="n">
-        <v>3.4</v>
+        <v>3.99</v>
       </c>
       <c r="N14" t="n">
-        <v>2.4</v>
+        <v>1.57</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.93</v>
+        <v>1.82</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>5.5</v>
+        <v>2.9</v>
       </c>
       <c r="M16" t="n">
-        <v>3.99</v>
+        <v>3.4</v>
       </c>
       <c r="N16" t="n">
-        <v>1.57</v>
+        <v>2.4</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.92</v>
+        <v>1.87</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.82</v>
+        <v>1.93</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>

--- a/jogos_2026-01-02.xlsx
+++ b/jogos_2026-01-02.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="G4" t="n">

--- a/jogos_2026-01-02.xlsx
+++ b/jogos_2026-01-02.xlsx
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1418,16 +1418,16 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE8" t="n">
         <v>0</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1537,16 +1537,16 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>5.5</v>
+        <v>2.9</v>
       </c>
       <c r="M14" t="n">
-        <v>3.99</v>
+        <v>3.4</v>
       </c>
       <c r="N14" t="n">
-        <v>1.57</v>
+        <v>2.4</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.92</v>
+        <v>1.87</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.82</v>
+        <v>1.93</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.9</v>
+        <v>5.5</v>
       </c>
       <c r="M16" t="n">
-        <v>3.4</v>
+        <v>3.99</v>
       </c>
       <c r="N16" t="n">
-        <v>2.4</v>
+        <v>1.57</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.93</v>
+        <v>1.82</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>

--- a/jogos_2026-01-02.xlsx
+++ b/jogos_2026-01-02.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>

--- a/jogos_2026-01-02.xlsx
+++ b/jogos_2026-01-02.xlsx
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.9</v>
+        <v>5.5</v>
       </c>
       <c r="M15" t="n">
-        <v>3.4</v>
+        <v>3.99</v>
       </c>
       <c r="N15" t="n">
-        <v>2.4</v>
+        <v>1.57</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.93</v>
+        <v>1.82</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>3.99</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>

--- a/jogos_2026-01-02.xlsx
+++ b/jogos_2026-01-02.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1418,16 +1418,16 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
         <v>0</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1537,16 +1537,16 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE9" t="n">
         <v>0</v>

--- a/jogos_2026-01-02.xlsx
+++ b/jogos_2026-01-02.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1418,16 +1418,16 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE8" t="n">
         <v>0</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1537,16 +1537,16 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3.99</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>

--- a/jogos_2026-01-02.xlsx
+++ b/jogos_2026-01-02.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>3.99</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>

--- a/jogos_2026-01-02.xlsx
+++ b/jogos_2026-01-02.xlsx
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1418,16 +1418,16 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
         <v>0</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1537,16 +1537,16 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE9" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>

--- a/jogos_2026-01-02.xlsx
+++ b/jogos_2026-01-02.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1418,16 +1418,16 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE8" t="n">
         <v>0</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1537,16 +1537,16 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
         <v>0</v>

--- a/jogos_2026-01-02.xlsx
+++ b/jogos_2026-01-02.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>5.8</v>
+        <v>6.3</v>
       </c>
       <c r="M12" t="n">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="N12" t="n">
-        <v>1.58</v>
+        <v>1.52</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>5.5</v>
+        <v>2.9</v>
       </c>
       <c r="M15" t="n">
-        <v>3.99</v>
+        <v>3.4</v>
       </c>
       <c r="N15" t="n">
-        <v>1.57</v>
+        <v>2.4</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.92</v>
+        <v>1.87</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.82</v>
+        <v>1.93</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.9</v>
+        <v>5.5</v>
       </c>
       <c r="M16" t="n">
-        <v>3.4</v>
+        <v>3.99</v>
       </c>
       <c r="N16" t="n">
-        <v>2.4</v>
+        <v>1.57</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.93</v>
+        <v>1.82</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="M18" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="N18" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>

--- a/jogos_2026-01-02.xlsx
+++ b/jogos_2026-01-02.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1418,16 +1418,16 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
         <v>0</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1537,16 +1537,16 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE9" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.46</v>
+        <v>2.9</v>
       </c>
       <c r="M14" t="n">
-        <v>2.95</v>
+        <v>3.4</v>
       </c>
       <c r="N14" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.9</v>
+        <v>2.46</v>
       </c>
       <c r="M15" t="n">
-        <v>3.4</v>
+        <v>2.95</v>
       </c>
       <c r="N15" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>

--- a/jogos_2026-01-02.xlsx
+++ b/jogos_2026-01-02.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1418,16 +1418,16 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE8" t="n">
         <v>0</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1537,16 +1537,16 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.9</v>
+        <v>5.5</v>
       </c>
       <c r="M14" t="n">
-        <v>3.4</v>
+        <v>3.99</v>
       </c>
       <c r="N14" t="n">
-        <v>2.4</v>
+        <v>1.57</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.93</v>
+        <v>1.82</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>5.5</v>
+        <v>2.76</v>
       </c>
       <c r="M16" t="n">
-        <v>3.99</v>
+        <v>3.33</v>
       </c>
       <c r="N16" t="n">
-        <v>1.57</v>
+        <v>2.46</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.82</v>
+        <v>1.89</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>

--- a/jogos_2026-01-02.xlsx
+++ b/jogos_2026-01-02.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>5.5</v>
+        <v>2.76</v>
       </c>
       <c r="M14" t="n">
-        <v>3.99</v>
+        <v>3.33</v>
       </c>
       <c r="N14" t="n">
-        <v>1.57</v>
+        <v>2.46</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.82</v>
+        <v>1.89</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.46</v>
+        <v>5.5</v>
       </c>
       <c r="M15" t="n">
-        <v>2.95</v>
+        <v>3.99</v>
       </c>
       <c r="N15" t="n">
-        <v>2.8</v>
+        <v>1.57</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.76</v>
+        <v>2.46</v>
       </c>
       <c r="M16" t="n">
-        <v>3.33</v>
+        <v>2.95</v>
       </c>
       <c r="N16" t="n">
-        <v>2.46</v>
+        <v>2.8</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>

--- a/jogos_2026-01-02.xlsx
+++ b/jogos_2026-01-02.xlsx
@@ -659,73 +659,73 @@
         </is>
       </c>
       <c r="L2" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="M2" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="N2" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="O2" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="P2" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S2" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V2" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="AA2" t="n">
         <v>1.7</v>
       </c>
-      <c r="M2" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="N2" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V2" t="n">
-        <v>0</v>
-      </c>
-      <c r="W2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>1.65</v>
-      </c>
       <c r="AB2" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46024.23263888889</v>
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="G4" t="n">

--- a/jogos_2026-01-02.xlsx
+++ b/jogos_2026-01-02.xlsx
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1418,16 +1418,16 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
         <v>0</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1537,16 +1537,16 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE9" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>5.5</v>
+        <v>2.46</v>
       </c>
       <c r="M15" t="n">
-        <v>3.99</v>
+        <v>2.95</v>
       </c>
       <c r="N15" t="n">
-        <v>1.57</v>
+        <v>2.8</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.46</v>
+        <v>5.5</v>
       </c>
       <c r="M16" t="n">
-        <v>2.95</v>
+        <v>3.99</v>
       </c>
       <c r="N16" t="n">
-        <v>2.8</v>
+        <v>1.57</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>

--- a/jogos_2026-01-02.xlsx
+++ b/jogos_2026-01-02.xlsx
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="M2" t="n">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="N2" t="n">
-        <v>3.91</v>
+        <v>4.5</v>
       </c>
       <c r="O2" t="n">
         <v>2.26</v>
@@ -704,10 +704,10 @@
         <v>3.98</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="AC2" t="n">
         <v>2.57</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.76</v>
+        <v>2.4</v>
       </c>
       <c r="M14" t="n">
-        <v>3.33</v>
+        <v>3.1</v>
       </c>
       <c r="N14" t="n">
-        <v>2.46</v>
+        <v>2.8</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.85</v>
+        <v>2.25</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.89</v>
+        <v>1.58</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.46</v>
+        <v>5.5</v>
       </c>
       <c r="M15" t="n">
-        <v>2.95</v>
+        <v>3.99</v>
       </c>
       <c r="N15" t="n">
-        <v>2.8</v>
+        <v>1.57</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>5.5</v>
+        <v>2.76</v>
       </c>
       <c r="M16" t="n">
-        <v>3.99</v>
+        <v>3.33</v>
       </c>
       <c r="N16" t="n">
-        <v>1.57</v>
+        <v>2.46</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.82</v>
+        <v>1.89</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>

--- a/jogos_2026-01-02.xlsx
+++ b/jogos_2026-01-02.xlsx
@@ -659,19 +659,19 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="M2" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="N2" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="O2" t="n">
         <v>2.26</v>
       </c>
       <c r="P2" t="n">
-        <v>2.23</v>
+        <v>2.26</v>
       </c>
       <c r="Q2" t="n">
         <v>4.7</v>
@@ -689,7 +689,7 @@
         <v>1.5</v>
       </c>
       <c r="V2" t="n">
-        <v>5.5</v>
+        <v>5.55</v>
       </c>
       <c r="W2" t="n">
         <v>1.08</v>
@@ -701,19 +701,19 @@
         <v>1.17</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.98</v>
+        <v>4</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AC2" t="n">
         <v>2.57</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="AE2" t="n">
         <v>1.63</v>
@@ -722,10 +722,10 @@
         <v>2.14</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46024.23263888889</v>

--- a/jogos_2026-01-02.xlsx
+++ b/jogos_2026-01-02.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1501,40 +1501,40 @@
         <v>5.9</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>7.15</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA9" t="n">
         <v>1.57</v>
@@ -1549,16 +1549,16 @@
         <v>1.53</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46024.53125</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.4</v>
+        <v>2.76</v>
       </c>
       <c r="M14" t="n">
-        <v>3.1</v>
+        <v>3.33</v>
       </c>
       <c r="N14" t="n">
-        <v>2.8</v>
+        <v>2.46</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.25</v>
+        <v>1.85</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.58</v>
+        <v>1.89</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.76</v>
+        <v>2.4</v>
       </c>
       <c r="M16" t="n">
-        <v>3.33</v>
+        <v>3.1</v>
       </c>
       <c r="N16" t="n">
-        <v>2.46</v>
+        <v>2.8</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.85</v>
+        <v>2.25</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.89</v>
+        <v>1.58</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>

--- a/jogos_2026-01-02.xlsx
+++ b/jogos_2026-01-02.xlsx
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>7.15</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46024.53125</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>7.15</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>4.95</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46024.53125</v>
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>6.3</v>
+        <v>6.35</v>
       </c>
       <c r="M12" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="N12" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>5.13</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.95</v>
+        <v>2.01</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46024.65625</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.76</v>
+        <v>6</v>
       </c>
       <c r="M14" t="n">
-        <v>3.33</v>
+        <v>3.9</v>
       </c>
       <c r="N14" t="n">
-        <v>2.46</v>
+        <v>1.53</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>4.94</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="AB14" t="n">
         <v>1.89</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46024.69791666666</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>5.5</v>
+        <v>2.4</v>
       </c>
       <c r="M15" t="n">
-        <v>3.99</v>
+        <v>3.1</v>
       </c>
       <c r="N15" t="n">
-        <v>1.57</v>
+        <v>2.8</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.92</v>
+        <v>2.25</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.82</v>
+        <v>1.58</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.4</v>
+        <v>2.76</v>
       </c>
       <c r="M16" t="n">
-        <v>3.1</v>
+        <v>3.33</v>
       </c>
       <c r="N16" t="n">
-        <v>2.8</v>
+        <v>2.46</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.25</v>
+        <v>1.85</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.58</v>
+        <v>1.89</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.02</v>
+        <v>1.86</v>
       </c>
       <c r="M18" t="n">
-        <v>3.3</v>
+        <v>3.43</v>
       </c>
       <c r="N18" t="n">
-        <v>3.7</v>
+        <v>4.06</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.2</v>
+        <v>2.07</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.6</v>
+        <v>1.76</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46024.73958333334</v>

--- a/jogos_2026-01-02.xlsx
+++ b/jogos_2026-01-02.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>6.35</v>
+        <v>6.3</v>
       </c>
       <c r="M12" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="N12" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="O12" t="n">
         <v>5.13</v>
@@ -1894,10 +1894,10 @@
         <v>3.4</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.01</v>
+        <v>1.95</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AC12" t="n">
         <v>3.4</v>
@@ -1977,40 +1977,40 @@
         <v>5.9</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AA13" t="n">
         <v>2.1</v>
@@ -2019,22 +2019,22 @@
         <v>1.65</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46024.6875</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="M14" t="n">
-        <v>3.9</v>
+        <v>3.1</v>
       </c>
       <c r="N14" t="n">
-        <v>1.53</v>
+        <v>2.8</v>
       </c>
       <c r="O14" t="n">
-        <v>4.94</v>
+        <v>3.12</v>
       </c>
       <c r="P14" t="n">
-        <v>2.23</v>
+        <v>1.94</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.12</v>
+        <v>3.72</v>
       </c>
       <c r="R14" t="n">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="S14" t="n">
-        <v>2.88</v>
+        <v>2.41</v>
       </c>
       <c r="T14" t="n">
-        <v>2.83</v>
+        <v>3.18</v>
       </c>
       <c r="U14" t="n">
-        <v>1.42</v>
+        <v>1.28</v>
       </c>
       <c r="V14" t="n">
-        <v>6.8</v>
+        <v>8.5</v>
       </c>
       <c r="W14" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X14" t="n">
         <v>1.07</v>
       </c>
-      <c r="X14" t="n">
-        <v>1.03</v>
-      </c>
       <c r="Y14" t="n">
-        <v>1.27</v>
+        <v>1.39</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.45</v>
+        <v>2.75</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.94</v>
+        <v>2.25</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.89</v>
+        <v>1.58</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.16</v>
+        <v>4.1</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.35</v>
+        <v>1.18</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.15</v>
+        <v>1.45</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46024.69791666666</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.4</v>
+        <v>5.5</v>
       </c>
       <c r="M15" t="n">
-        <v>3.1</v>
+        <v>3.99</v>
       </c>
       <c r="N15" t="n">
-        <v>2.8</v>
+        <v>1.57</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>4.94</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.25</v>
+        <v>1.92</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.58</v>
+        <v>1.82</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46024.69791666666</v>
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.86</v>
+        <v>2.02</v>
       </c>
       <c r="M18" t="n">
-        <v>3.43</v>
+        <v>3.3</v>
       </c>
       <c r="N18" t="n">
-        <v>4.06</v>
+        <v>3.7</v>
       </c>
       <c r="O18" t="n">
         <v>2.51</v>
@@ -2608,10 +2608,10 @@
         <v>3.15</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.07</v>
+        <v>2.2</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.76</v>
+        <v>1.6</v>
       </c>
       <c r="AC18" t="n">
         <v>4</v>

--- a/jogos_2026-01-02.xlsx
+++ b/jogos_2026-01-02.xlsx
@@ -659,22 +659,22 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="M2" t="n">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="N2" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="O2" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="P2" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="R2" t="n">
         <v>1.31</v>
@@ -683,13 +683,13 @@
         <v>3.15</v>
       </c>
       <c r="T2" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="U2" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="V2" t="n">
-        <v>5.55</v>
+        <v>5.5</v>
       </c>
       <c r="W2" t="n">
         <v>1.08</v>
@@ -704,7 +704,7 @@
         <v>4</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="AB2" t="n">
         <v>2.18</v>
@@ -713,19 +713,19 @@
         <v>2.57</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AF2" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="AG2" t="n">
         <v>1.27</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.07</v>
+        <v>2.02</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46024.23263888889</v>

--- a/jogos_2026-01-02.xlsx
+++ b/jogos_2026-01-02.xlsx
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.81</v>
+        <v>1.7</v>
       </c>
       <c r="M2" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="N2" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="O2" t="n">
         <v>2.28</v>
@@ -704,10 +704,10 @@
         <v>4</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="AC2" t="n">
         <v>2.57</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>7.15</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>4.95</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46024.53125</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>7.15</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46024.53125</v>
@@ -1873,25 +1873,25 @@
         <v>2.73</v>
       </c>
       <c r="T12" t="n">
-        <v>2.85</v>
+        <v>2.88</v>
       </c>
       <c r="U12" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="V12" t="n">
         <v>7.5</v>
       </c>
       <c r="W12" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X12" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.4</v>
+        <v>3.12</v>
       </c>
       <c r="AA12" t="n">
         <v>1.95</v>
@@ -1900,10 +1900,10 @@
         <v>1.75</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.4</v>
+        <v>3.24</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="AE12" t="n">
         <v>2.02</v>
@@ -1915,7 +1915,7 @@
         <v>1.26</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46024.65625</v>
@@ -1983,7 +1983,7 @@
         <v>2.06</v>
       </c>
       <c r="Q13" t="n">
-        <v>6.25</v>
+        <v>5.32</v>
       </c>
       <c r="R13" t="n">
         <v>1.46</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.4</v>
+        <v>5.5</v>
       </c>
       <c r="M14" t="n">
-        <v>3.1</v>
+        <v>3.99</v>
       </c>
       <c r="N14" t="n">
-        <v>2.8</v>
+        <v>1.57</v>
       </c>
       <c r="O14" t="n">
-        <v>3.12</v>
+        <v>4.94</v>
       </c>
       <c r="P14" t="n">
-        <v>1.94</v>
+        <v>2.23</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.72</v>
+        <v>2.12</v>
       </c>
       <c r="R14" t="n">
-        <v>1.47</v>
+        <v>1.41</v>
       </c>
       <c r="S14" t="n">
-        <v>2.41</v>
+        <v>2.88</v>
       </c>
       <c r="T14" t="n">
-        <v>3.18</v>
+        <v>2.83</v>
       </c>
       <c r="U14" t="n">
-        <v>1.28</v>
+        <v>1.42</v>
       </c>
       <c r="V14" t="n">
-        <v>8.5</v>
+        <v>6.5</v>
       </c>
       <c r="W14" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X14" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.39</v>
+        <v>1.27</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.75</v>
+        <v>3.55</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.25</v>
+        <v>1.92</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.58</v>
+        <v>1.82</v>
       </c>
       <c r="AC14" t="n">
-        <v>4.1</v>
+        <v>3.45</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.18</v>
+        <v>1.36</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.45</v>
+        <v>1.15</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46024.69791666666</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>5.5</v>
+        <v>2.4</v>
       </c>
       <c r="M15" t="n">
-        <v>3.99</v>
+        <v>3.1</v>
       </c>
       <c r="N15" t="n">
-        <v>1.57</v>
+        <v>2.8</v>
       </c>
       <c r="O15" t="n">
-        <v>4.94</v>
+        <v>3.12</v>
       </c>
       <c r="P15" t="n">
-        <v>2.23</v>
+        <v>1.94</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.12</v>
+        <v>3.72</v>
       </c>
       <c r="R15" t="n">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="S15" t="n">
-        <v>2.88</v>
+        <v>2.41</v>
       </c>
       <c r="T15" t="n">
-        <v>2.83</v>
+        <v>3.18</v>
       </c>
       <c r="U15" t="n">
-        <v>1.42</v>
+        <v>1.28</v>
       </c>
       <c r="V15" t="n">
-        <v>6.8</v>
+        <v>8.5</v>
       </c>
       <c r="W15" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X15" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.27</v>
+        <v>1.39</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.45</v>
+        <v>2.59</v>
       </c>
       <c r="AA15" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AE15" t="n">
         <v>1.92</v>
       </c>
-      <c r="AB15" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AF15" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.15</v>
+        <v>1.45</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46024.69791666666</v>
@@ -2334,40 +2334,40 @@
         <v>2.46</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA16" t="n">
         <v>1.85</v>
@@ -2376,22 +2376,22 @@
         <v>1.89</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46024.69791666666</v>
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46024.70833333334</v>
@@ -2587,10 +2587,10 @@
         <v>2.59</v>
       </c>
       <c r="T18" t="n">
-        <v>3.1</v>
+        <v>3.02</v>
       </c>
       <c r="U18" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="V18" t="n">
         <v>7</v>
@@ -2602,7 +2602,7 @@
         <v>1.07</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="Z18" t="n">
         <v>3.15</v>
@@ -2617,7 +2617,7 @@
         <v>4</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AE18" t="n">
         <v>1.88</v>

--- a/jogos_2026-01-02.xlsx
+++ b/jogos_2026-01-02.xlsx
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>7.15</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46024.53125</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>7.15</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>4.95</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46024.53125</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>5.5</v>
+        <v>2.4</v>
       </c>
       <c r="M14" t="n">
-        <v>3.99</v>
+        <v>3.1</v>
       </c>
       <c r="N14" t="n">
-        <v>1.57</v>
+        <v>2.8</v>
       </c>
       <c r="O14" t="n">
-        <v>4.94</v>
+        <v>3.12</v>
       </c>
       <c r="P14" t="n">
-        <v>2.23</v>
+        <v>1.94</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.12</v>
+        <v>3.72</v>
       </c>
       <c r="R14" t="n">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="S14" t="n">
-        <v>2.88</v>
+        <v>2.41</v>
       </c>
       <c r="T14" t="n">
-        <v>2.83</v>
+        <v>3.18</v>
       </c>
       <c r="U14" t="n">
-        <v>1.42</v>
+        <v>1.28</v>
       </c>
       <c r="V14" t="n">
-        <v>6.5</v>
+        <v>8.5</v>
       </c>
       <c r="W14" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X14" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.27</v>
+        <v>1.39</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.55</v>
+        <v>2.59</v>
       </c>
       <c r="AA14" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AE14" t="n">
         <v>1.92</v>
       </c>
-      <c r="AB14" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AF14" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.15</v>
+        <v>1.45</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46024.69791666666</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.4</v>
+        <v>2.76</v>
       </c>
       <c r="M15" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="N15" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="O15" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="Q15" t="n">
         <v>3.1</v>
       </c>
-      <c r="N15" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="O15" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="P15" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>3.72</v>
-      </c>
       <c r="R15" t="n">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="S15" t="n">
-        <v>2.41</v>
+        <v>2.89</v>
       </c>
       <c r="T15" t="n">
-        <v>3.18</v>
+        <v>2.81</v>
       </c>
       <c r="U15" t="n">
-        <v>1.28</v>
+        <v>1.43</v>
       </c>
       <c r="V15" t="n">
-        <v>8.5</v>
+        <v>7.3</v>
       </c>
       <c r="W15" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X15" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.39</v>
+        <v>1.25</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.59</v>
+        <v>3.6</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.25</v>
+        <v>1.85</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.58</v>
+        <v>1.89</v>
       </c>
       <c r="AC15" t="n">
-        <v>4.1</v>
+        <v>3.1</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.16</v>
+        <v>1.33</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.92</v>
+        <v>1.67</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.77</v>
+        <v>2.1</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46024.69791666666</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.76</v>
+        <v>5.5</v>
       </c>
       <c r="M16" t="n">
-        <v>3.33</v>
+        <v>3.99</v>
       </c>
       <c r="N16" t="n">
-        <v>2.46</v>
+        <v>1.57</v>
       </c>
       <c r="O16" t="n">
-        <v>3.42</v>
+        <v>4.94</v>
       </c>
       <c r="P16" t="n">
-        <v>2.09</v>
+        <v>2.23</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.1</v>
+        <v>2.12</v>
       </c>
       <c r="R16" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="S16" t="n">
-        <v>2.89</v>
+        <v>2.88</v>
       </c>
       <c r="T16" t="n">
-        <v>2.81</v>
+        <v>2.83</v>
       </c>
       <c r="U16" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="V16" t="n">
-        <v>7.3</v>
+        <v>6.5</v>
       </c>
       <c r="W16" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X16" t="n">
         <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.89</v>
+        <v>1.82</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.1</v>
+        <v>3.45</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.67</v>
+        <v>1.95</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.1</v>
+        <v>1.78</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.4</v>
+        <v>1.15</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46024.69791666666</v>

--- a/jogos_2026-01-02.xlsx
+++ b/jogos_2026-01-02.xlsx
@@ -659,37 +659,37 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.7</v>
+        <v>1.79</v>
       </c>
       <c r="M2" t="n">
-        <v>3.85</v>
+        <v>3.86</v>
       </c>
       <c r="N2" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="O2" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="P2" t="n">
-        <v>2.25</v>
+        <v>2.44</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.5</v>
+        <v>4.59</v>
       </c>
       <c r="R2" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="S2" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="T2" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="U2" t="n">
         <v>1.49</v>
       </c>
       <c r="V2" t="n">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="W2" t="n">
         <v>1.08</v>
@@ -698,34 +698,34 @@
         <v>1.02</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="Z2" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="AA2" t="n">
         <v>1.65</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.57</v>
+        <v>2.64</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="AF2" t="n">
-        <v>2.16</v>
+        <v>2.13</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46024.23263888889</v>
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>7.15</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>4.95</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46024.53125</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>7.15</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46024.53125</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.4</v>
+        <v>2.76</v>
       </c>
       <c r="M14" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="N14" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="O14" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="Q14" t="n">
         <v>3.1</v>
       </c>
-      <c r="N14" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="O14" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="P14" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>3.72</v>
-      </c>
       <c r="R14" t="n">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="S14" t="n">
-        <v>2.41</v>
+        <v>2.89</v>
       </c>
       <c r="T14" t="n">
-        <v>3.18</v>
+        <v>2.81</v>
       </c>
       <c r="U14" t="n">
-        <v>1.28</v>
+        <v>1.43</v>
       </c>
       <c r="V14" t="n">
-        <v>8.5</v>
+        <v>7.3</v>
       </c>
       <c r="W14" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X14" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.39</v>
+        <v>1.25</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.59</v>
+        <v>3.6</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.25</v>
+        <v>1.85</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.58</v>
+        <v>1.89</v>
       </c>
       <c r="AC14" t="n">
-        <v>4.1</v>
+        <v>3.1</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.16</v>
+        <v>1.33</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.92</v>
+        <v>1.67</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.77</v>
+        <v>2.1</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46024.69791666666</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.76</v>
+        <v>5.5</v>
       </c>
       <c r="M15" t="n">
-        <v>3.33</v>
+        <v>3.99</v>
       </c>
       <c r="N15" t="n">
-        <v>2.46</v>
+        <v>1.57</v>
       </c>
       <c r="O15" t="n">
-        <v>3.42</v>
+        <v>4.94</v>
       </c>
       <c r="P15" t="n">
-        <v>2.09</v>
+        <v>2.23</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.1</v>
+        <v>2.12</v>
       </c>
       <c r="R15" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="S15" t="n">
-        <v>2.89</v>
+        <v>2.88</v>
       </c>
       <c r="T15" t="n">
-        <v>2.81</v>
+        <v>2.83</v>
       </c>
       <c r="U15" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="V15" t="n">
-        <v>7.3</v>
+        <v>6.5</v>
       </c>
       <c r="W15" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X15" t="n">
         <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.89</v>
+        <v>1.82</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.1</v>
+        <v>3.45</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.67</v>
+        <v>1.95</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.1</v>
+        <v>1.78</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.4</v>
+        <v>1.15</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46024.69791666666</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>5.5</v>
+        <v>2.4</v>
       </c>
       <c r="M16" t="n">
-        <v>3.99</v>
+        <v>3.1</v>
       </c>
       <c r="N16" t="n">
-        <v>1.57</v>
+        <v>2.8</v>
       </c>
       <c r="O16" t="n">
-        <v>4.94</v>
+        <v>3.12</v>
       </c>
       <c r="P16" t="n">
-        <v>2.23</v>
+        <v>1.94</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.12</v>
+        <v>3.72</v>
       </c>
       <c r="R16" t="n">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="S16" t="n">
-        <v>2.88</v>
+        <v>2.41</v>
       </c>
       <c r="T16" t="n">
-        <v>2.83</v>
+        <v>3.18</v>
       </c>
       <c r="U16" t="n">
-        <v>1.42</v>
+        <v>1.28</v>
       </c>
       <c r="V16" t="n">
-        <v>6.5</v>
+        <v>8.5</v>
       </c>
       <c r="W16" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X16" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.27</v>
+        <v>1.39</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.55</v>
+        <v>2.59</v>
       </c>
       <c r="AA16" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AE16" t="n">
         <v>1.92</v>
       </c>
-      <c r="AB16" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AF16" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.15</v>
+        <v>1.45</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46024.69791666666</v>

--- a/jogos_2026-01-02.xlsx
+++ b/jogos_2026-01-02.xlsx
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.79</v>
+        <v>1.7</v>
       </c>
       <c r="M2" t="n">
-        <v>3.86</v>
+        <v>3.85</v>
       </c>
       <c r="N2" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="O2" t="n">
         <v>2.3</v>
@@ -707,7 +707,7 @@
         <v>1.65</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="AC2" t="n">
         <v>2.64</v>
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>4.93</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46024.41319444445</v>
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1025,64 +1025,64 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>4.89</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46024.41666666666</v>
@@ -1528,7 +1528,7 @@
         <v>1.11</v>
       </c>
       <c r="X9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y9" t="n">
         <v>1.14</v>
@@ -1558,7 +1558,7 @@
         <v>1.12</v>
       </c>
       <c r="AH9" t="n">
-        <v>3.1</v>
+        <v>2.89</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46024.53125</v>
@@ -1861,34 +1861,34 @@
         <v>5.13</v>
       </c>
       <c r="P12" t="n">
-        <v>2.17</v>
+        <v>2.08</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="R12" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="S12" t="n">
         <v>2.73</v>
       </c>
       <c r="T12" t="n">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="U12" t="n">
         <v>1.36</v>
       </c>
       <c r="V12" t="n">
-        <v>7.5</v>
+        <v>6.75</v>
       </c>
       <c r="W12" t="n">
         <v>1.04</v>
       </c>
       <c r="X12" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="Z12" t="n">
         <v>3.12</v>
@@ -1906,16 +1906,16 @@
         <v>1.26</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AF12" t="n">
         <v>1.71</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.26</v>
+        <v>2.45</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46024.65625</v>
@@ -1977,25 +1977,25 @@
         <v>5.9</v>
       </c>
       <c r="O13" t="n">
-        <v>2.04</v>
+        <v>2.18</v>
       </c>
       <c r="P13" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="Q13" t="n">
-        <v>5.32</v>
+        <v>5.25</v>
       </c>
       <c r="R13" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="S13" t="n">
-        <v>2.53</v>
+        <v>2.7</v>
       </c>
       <c r="T13" t="n">
         <v>3.1</v>
       </c>
       <c r="U13" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="V13" t="n">
         <v>7.5</v>
@@ -2007,10 +2007,10 @@
         <v>1.03</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="AA13" t="n">
         <v>2.1</v>
@@ -2096,31 +2096,31 @@
         <v>2.46</v>
       </c>
       <c r="O14" t="n">
-        <v>3.42</v>
+        <v>3</v>
       </c>
       <c r="P14" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="Q14" t="n">
         <v>3.1</v>
       </c>
       <c r="R14" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="S14" t="n">
         <v>2.89</v>
       </c>
       <c r="T14" t="n">
-        <v>2.81</v>
+        <v>2.65</v>
       </c>
       <c r="U14" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="V14" t="n">
-        <v>7.3</v>
+        <v>6.25</v>
       </c>
       <c r="W14" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X14" t="n">
         <v>1.01</v>
@@ -2150,7 +2150,7 @@
         <v>2.1</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AH14" t="n">
         <v>1.4</v>
@@ -2215,28 +2215,28 @@
         <v>1.57</v>
       </c>
       <c r="O15" t="n">
-        <v>4.94</v>
+        <v>6</v>
       </c>
       <c r="P15" t="n">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="Q15" t="n">
         <v>2.12</v>
       </c>
       <c r="R15" t="n">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="S15" t="n">
-        <v>2.88</v>
+        <v>2.91</v>
       </c>
       <c r="T15" t="n">
-        <v>2.83</v>
+        <v>2.7</v>
       </c>
       <c r="U15" t="n">
         <v>1.42</v>
       </c>
       <c r="V15" t="n">
-        <v>6.5</v>
+        <v>6.8</v>
       </c>
       <c r="W15" t="n">
         <v>1.07</v>
@@ -2248,7 +2248,7 @@
         <v>1.27</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.55</v>
+        <v>3.36</v>
       </c>
       <c r="AA15" t="n">
         <v>1.92</v>
@@ -2257,10 +2257,10 @@
         <v>1.82</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AE15" t="n">
         <v>1.95</v>
@@ -2269,7 +2269,7 @@
         <v>1.78</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AH15" t="n">
         <v>1.15</v>
@@ -2337,7 +2337,7 @@
         <v>3.12</v>
       </c>
       <c r="P16" t="n">
-        <v>1.94</v>
+        <v>2.04</v>
       </c>
       <c r="Q16" t="n">
         <v>3.72</v>
@@ -2364,7 +2364,7 @@
         <v>1.04</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="Z16" t="n">
         <v>2.59</v>
@@ -2572,40 +2572,40 @@
         <v>3.7</v>
       </c>
       <c r="O18" t="n">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="P18" t="n">
-        <v>2.03</v>
+        <v>2.08</v>
       </c>
       <c r="Q18" t="n">
         <v>4.7</v>
       </c>
       <c r="R18" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="S18" t="n">
-        <v>2.59</v>
+        <v>2.8</v>
       </c>
       <c r="T18" t="n">
-        <v>3.02</v>
+        <v>2.9</v>
       </c>
       <c r="U18" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="V18" t="n">
         <v>7</v>
       </c>
       <c r="W18" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X18" t="n">
         <v>1.03</v>
       </c>
-      <c r="X18" t="n">
-        <v>1.07</v>
-      </c>
       <c r="Y18" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="AA18" t="n">
         <v>2.2</v>
@@ -2617,7 +2617,7 @@
         <v>4</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.26</v>
+        <v>1.19</v>
       </c>
       <c r="AE18" t="n">
         <v>1.88</v>
@@ -2626,7 +2626,7 @@
         <v>1.82</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AH18" t="n">
         <v>1.88</v>

--- a/jogos_2026-01-02.xlsx
+++ b/jogos_2026-01-02.xlsx
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.7</v>
+        <v>1.79</v>
       </c>
       <c r="M2" t="n">
-        <v>3.85</v>
+        <v>3.86</v>
       </c>
       <c r="N2" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="O2" t="n">
         <v>2.3</v>
@@ -698,22 +698,22 @@
         <v>1.02</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.85</v>
+        <v>3.94</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AC2" t="n">
         <v>2.64</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="AE2" t="n">
         <v>1.64</v>
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="M3" t="n">
-        <v>4.15</v>
+        <v>3.9</v>
       </c>
       <c r="N3" t="n">
-        <v>4.6</v>
+        <v>4.61</v>
       </c>
       <c r="O3" t="n">
         <v>2.13</v>
@@ -814,25 +814,25 @@
         <v>1.09</v>
       </c>
       <c r="X3" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y3" t="n">
         <v>1.13</v>
       </c>
       <c r="Z3" t="n">
-        <v>4.5</v>
+        <v>4.55</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AB3" t="n">
         <v>2.25</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.41</v>
+        <v>2.38</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="AE3" t="n">
         <v>1.59</v>
@@ -1144,64 +1144,64 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>4.41</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46024.4375</v>
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.45</v>
+        <v>1.29</v>
       </c>
       <c r="M9" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="N9" t="n">
-        <v>5.9</v>
+        <v>7.9</v>
       </c>
       <c r="O9" t="n">
         <v>1.8</v>
@@ -1540,13 +1540,13 @@
         <v>1.57</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.38</v>
+        <v>2.28</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AE9" t="n">
         <v>1.82</v>
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.76</v>
+        <v>5.5</v>
       </c>
       <c r="M14" t="n">
-        <v>3.33</v>
+        <v>3.99</v>
       </c>
       <c r="N14" t="n">
-        <v>2.46</v>
+        <v>1.57</v>
       </c>
       <c r="O14" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="P14" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.1</v>
+        <v>2.12</v>
       </c>
       <c r="R14" t="n">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="S14" t="n">
-        <v>2.89</v>
+        <v>2.91</v>
       </c>
       <c r="T14" t="n">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="U14" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="V14" t="n">
-        <v>6.25</v>
+        <v>6.8</v>
       </c>
       <c r="W14" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X14" t="n">
         <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.6</v>
+        <v>3.36</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.89</v>
+        <v>1.82</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.67</v>
+        <v>1.95</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.1</v>
+        <v>1.78</v>
       </c>
       <c r="AG14" t="n">
         <v>1.25</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.4</v>
+        <v>1.15</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46024.69791666666</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>5.5</v>
+        <v>2.4</v>
       </c>
       <c r="M15" t="n">
-        <v>3.99</v>
+        <v>3.1</v>
       </c>
       <c r="N15" t="n">
-        <v>1.57</v>
+        <v>2.8</v>
       </c>
       <c r="O15" t="n">
-        <v>6</v>
+        <v>3.12</v>
       </c>
       <c r="P15" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V15" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AA15" t="n">
         <v>2.25</v>
       </c>
-      <c r="Q15" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="V15" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="AA15" t="n">
+      <c r="AB15" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AE15" t="n">
         <v>1.92</v>
       </c>
-      <c r="AB15" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AF15" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.15</v>
+        <v>1.45</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46024.69791666666</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.4</v>
+        <v>2.76</v>
       </c>
       <c r="M16" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="N16" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="O16" t="n">
+        <v>3</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q16" t="n">
         <v>3.1</v>
       </c>
-      <c r="N16" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="O16" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="P16" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>3.72</v>
-      </c>
       <c r="R16" t="n">
-        <v>1.47</v>
+        <v>1.41</v>
       </c>
       <c r="S16" t="n">
-        <v>2.41</v>
+        <v>2.89</v>
       </c>
       <c r="T16" t="n">
-        <v>3.18</v>
+        <v>2.65</v>
       </c>
       <c r="U16" t="n">
-        <v>1.28</v>
+        <v>1.44</v>
       </c>
       <c r="V16" t="n">
-        <v>8.5</v>
+        <v>6.25</v>
       </c>
       <c r="W16" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="X16" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.59</v>
+        <v>3.6</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.25</v>
+        <v>1.85</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.58</v>
+        <v>1.89</v>
       </c>
       <c r="AC16" t="n">
-        <v>4.1</v>
+        <v>3.1</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.16</v>
+        <v>1.33</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.92</v>
+        <v>1.67</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.77</v>
+        <v>2.1</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46024.69791666666</v>

--- a/jogos_2026-01-02.xlsx
+++ b/jogos_2026-01-02.xlsx
@@ -1046,10 +1046,10 @@
         <v>1.39</v>
       </c>
       <c r="V5" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="W5" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X5" t="n">
         <v>1.01</v>
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>6.3</v>
+        <v>5.75</v>
       </c>
       <c r="M12" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="N12" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="O12" t="n">
         <v>5.13</v>
@@ -1876,7 +1876,7 @@
         <v>2.75</v>
       </c>
       <c r="U12" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="V12" t="n">
         <v>6.75</v>
@@ -1897,7 +1897,7 @@
         <v>1.95</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AC12" t="n">
         <v>3.24</v>
@@ -1912,7 +1912,7 @@
         <v>1.71</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
       <c r="AH12" t="n">
         <v>1.11</v>
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="M13" t="n">
-        <v>3.62</v>
+        <v>3.5</v>
       </c>
       <c r="N13" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="O13" t="n">
         <v>2.18</v>
@@ -2013,10 +2013,10 @@
         <v>2.9</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="AC13" t="n">
         <v>3.62</v>
@@ -2025,16 +2025,16 @@
         <v>1.21</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AG13" t="n">
         <v>1.28</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.27</v>
+        <v>2.29</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46024.6875</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>5.5</v>
+        <v>2.47</v>
       </c>
       <c r="M14" t="n">
-        <v>3.99</v>
+        <v>3</v>
       </c>
       <c r="N14" t="n">
-        <v>1.57</v>
+        <v>2.8</v>
       </c>
       <c r="O14" t="n">
-        <v>6</v>
+        <v>3.14</v>
       </c>
       <c r="P14" t="n">
-        <v>2.25</v>
+        <v>2.04</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.12</v>
+        <v>3.68</v>
       </c>
       <c r="R14" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="S14" t="n">
-        <v>2.91</v>
+        <v>2.44</v>
       </c>
       <c r="T14" t="n">
-        <v>2.7</v>
+        <v>3.18</v>
       </c>
       <c r="U14" t="n">
-        <v>1.42</v>
+        <v>1.28</v>
       </c>
       <c r="V14" t="n">
-        <v>6.8</v>
+        <v>8.5</v>
       </c>
       <c r="W14" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X14" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.36</v>
+        <v>2.66</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.92</v>
+        <v>2.23</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.82</v>
+        <v>1.58</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.95</v>
+        <v>1.89</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.15</v>
+        <v>1.44</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46024.69791666666</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.4</v>
+        <v>5.5</v>
       </c>
       <c r="M15" t="n">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="N15" t="n">
-        <v>2.8</v>
+        <v>1.55</v>
       </c>
       <c r="O15" t="n">
-        <v>3.12</v>
+        <v>6</v>
       </c>
       <c r="P15" t="n">
-        <v>2.04</v>
+        <v>2.25</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.72</v>
+        <v>2.12</v>
       </c>
       <c r="R15" t="n">
-        <v>1.47</v>
+        <v>1.33</v>
       </c>
       <c r="S15" t="n">
-        <v>2.41</v>
+        <v>2.91</v>
       </c>
       <c r="T15" t="n">
-        <v>3.18</v>
+        <v>2.7</v>
       </c>
       <c r="U15" t="n">
-        <v>1.28</v>
+        <v>1.42</v>
       </c>
       <c r="V15" t="n">
-        <v>8.5</v>
+        <v>6.8</v>
       </c>
       <c r="W15" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X15" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.38</v>
+        <v>1.27</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.59</v>
+        <v>3.71</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.58</v>
+        <v>1.92</v>
       </c>
       <c r="AC15" t="n">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.16</v>
+        <v>1.3</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.45</v>
+        <v>1.15</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46024.69791666666</v>
@@ -2325,61 +2325,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="M16" t="n">
-        <v>3.33</v>
+        <v>3.35</v>
       </c>
       <c r="N16" t="n">
-        <v>2.46</v>
+        <v>2.6</v>
       </c>
       <c r="O16" t="n">
         <v>3</v>
       </c>
       <c r="P16" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="Q16" t="n">
         <v>3.1</v>
       </c>
       <c r="R16" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="S16" t="n">
-        <v>2.89</v>
+        <v>2.85</v>
       </c>
       <c r="T16" t="n">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="U16" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="V16" t="n">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
       <c r="W16" t="n">
         <v>1.1</v>
       </c>
       <c r="X16" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.85</v>
+        <v>1.99</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AE16" t="n">
         <v>1.67</v>
@@ -2444,16 +2444,16 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="M17" t="n">
-        <v>2.86</v>
+        <v>3.05</v>
       </c>
       <c r="N17" t="n">
-        <v>3.55</v>
+        <v>3.9</v>
       </c>
       <c r="O17" t="n">
-        <v>2.75</v>
+        <v>2.96</v>
       </c>
       <c r="P17" t="n">
         <v>1.91</v>
@@ -2462,10 +2462,10 @@
         <v>4.75</v>
       </c>
       <c r="R17" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="S17" t="n">
-        <v>2.18</v>
+        <v>2.31</v>
       </c>
       <c r="T17" t="n">
         <v>4.2</v>
@@ -2480,13 +2480,13 @@
         <v>1</v>
       </c>
       <c r="X17" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.65</v>
+        <v>1.74</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.15</v>
+        <v>2.26</v>
       </c>
       <c r="AA17" t="n">
         <v>2.93</v>
@@ -2498,19 +2498,19 @@
         <v>5.8</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AE17" t="n">
-        <v>2.68</v>
+        <v>2.38</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46024.70833333334</v>
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.02</v>
+        <v>1.94</v>
       </c>
       <c r="M18" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="N18" t="n">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="O18" t="n">
         <v>2.5</v>
@@ -2584,7 +2584,7 @@
         <v>1.42</v>
       </c>
       <c r="S18" t="n">
-        <v>2.8</v>
+        <v>2.59</v>
       </c>
       <c r="T18" t="n">
         <v>2.9</v>
@@ -2596,28 +2596,28 @@
         <v>7</v>
       </c>
       <c r="W18" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X18" t="n">
         <v>1.03</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="Z18" t="n">
-        <v>3</v>
+        <v>2.89</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.2</v>
+        <v>2.07</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.6</v>
+        <v>1.76</v>
       </c>
       <c r="AC18" t="n">
         <v>4</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AE18" t="n">
         <v>1.88</v>

--- a/jogos_2026-01-02.xlsx
+++ b/jogos_2026-01-02.xlsx
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.79</v>
+        <v>1.7</v>
       </c>
       <c r="M2" t="n">
-        <v>3.86</v>
+        <v>3.85</v>
       </c>
       <c r="N2" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="O2" t="n">
         <v>2.3</v>
@@ -704,10 +704,10 @@
         <v>3.94</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AC2" t="n">
         <v>2.64</v>
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>4.61</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.93</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46024.41319444445</v>
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>4.61</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>4.93</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46024.41319444445</v>
@@ -1849,19 +1849,19 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>5.75</v>
+        <v>6.4</v>
       </c>
       <c r="M12" t="n">
         <v>4.2</v>
       </c>
       <c r="N12" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="O12" t="n">
-        <v>5.13</v>
+        <v>6.69</v>
       </c>
       <c r="P12" t="n">
-        <v>2.08</v>
+        <v>2.17</v>
       </c>
       <c r="Q12" t="n">
         <v>2.08</v>
@@ -1897,7 +1897,7 @@
         <v>1.95</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AC12" t="n">
         <v>3.24</v>
@@ -1906,16 +1906,16 @@
         <v>1.26</v>
       </c>
       <c r="AE12" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AF12" t="n">
         <v>1.71</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.48</v>
+        <v>1.26</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46024.65625</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.47</v>
+        <v>2.8</v>
       </c>
       <c r="M14" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="N14" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="O14" t="n">
         <v>3</v>
       </c>
-      <c r="N14" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="O14" t="n">
-        <v>3.14</v>
-      </c>
       <c r="P14" t="n">
-        <v>2.04</v>
+        <v>2.09</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.68</v>
+        <v>3.1</v>
       </c>
       <c r="R14" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="S14" t="n">
-        <v>2.44</v>
+        <v>2.85</v>
       </c>
       <c r="T14" t="n">
-        <v>3.18</v>
+        <v>2.75</v>
       </c>
       <c r="U14" t="n">
-        <v>1.28</v>
+        <v>1.42</v>
       </c>
       <c r="V14" t="n">
-        <v>8.5</v>
+        <v>6.5</v>
       </c>
       <c r="W14" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="X14" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.66</v>
+        <v>3.4</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.23</v>
+        <v>1.99</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.58</v>
+        <v>1.8</v>
       </c>
       <c r="AC14" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.89</v>
+        <v>1.67</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46024.69791666666</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>5.5</v>
+        <v>2.65</v>
       </c>
       <c r="M15" t="n">
-        <v>4</v>
+        <v>3.05</v>
       </c>
       <c r="N15" t="n">
-        <v>1.55</v>
+        <v>2.48</v>
       </c>
       <c r="O15" t="n">
-        <v>6</v>
+        <v>3.44</v>
       </c>
       <c r="P15" t="n">
-        <v>2.25</v>
+        <v>2.04</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.12</v>
+        <v>3.16</v>
       </c>
       <c r="R15" t="n">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
       <c r="S15" t="n">
-        <v>2.91</v>
+        <v>2.47</v>
       </c>
       <c r="T15" t="n">
-        <v>2.7</v>
+        <v>3.08</v>
       </c>
       <c r="U15" t="n">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="V15" t="n">
-        <v>6.8</v>
+        <v>8.1</v>
       </c>
       <c r="W15" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X15" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.71</v>
+        <v>2.74</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.95</v>
+        <v>2.16</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.92</v>
+        <v>1.62</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.4</v>
+        <v>3.82</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.78</v>
+        <v>1.84</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.15</v>
+        <v>1.37</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46024.69791666666</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.8</v>
+        <v>5.5</v>
       </c>
       <c r="M16" t="n">
-        <v>3.35</v>
+        <v>4</v>
       </c>
       <c r="N16" t="n">
-        <v>2.6</v>
+        <v>1.55</v>
       </c>
       <c r="O16" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="P16" t="n">
-        <v>2.09</v>
+        <v>2.25</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.1</v>
+        <v>2.12</v>
       </c>
       <c r="R16" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="S16" t="n">
-        <v>2.85</v>
+        <v>2.91</v>
       </c>
       <c r="T16" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="U16" t="n">
         <v>1.42</v>
       </c>
       <c r="V16" t="n">
-        <v>6.5</v>
+        <v>6.8</v>
       </c>
       <c r="W16" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X16" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="Z16" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AC16" t="n">
         <v>3.4</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>3.3</v>
       </c>
       <c r="AD16" t="n">
         <v>1.3</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.67</v>
+        <v>1.95</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.1</v>
+        <v>1.78</v>
       </c>
       <c r="AG16" t="n">
         <v>1.25</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.4</v>
+        <v>1.15</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46024.69791666666</v>
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="M18" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="N18" t="n">
-        <v>4.1</v>
+        <v>4.12</v>
       </c>
       <c r="O18" t="n">
         <v>2.5</v>
@@ -2587,7 +2587,7 @@
         <v>2.59</v>
       </c>
       <c r="T18" t="n">
-        <v>2.9</v>
+        <v>3.02</v>
       </c>
       <c r="U18" t="n">
         <v>1.36</v>
@@ -2602,13 +2602,13 @@
         <v>1.03</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="Z18" t="n">
         <v>2.89</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.07</v>
+        <v>2.14</v>
       </c>
       <c r="AB18" t="n">
         <v>1.76</v>
@@ -2626,10 +2626,10 @@
         <v>1.82</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46024.73958333334</v>

--- a/jogos_2026-01-02.xlsx
+++ b/jogos_2026-01-02.xlsx
@@ -1067,7 +1067,7 @@
         <v>1.85</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.97</v>
+        <v>3.05</v>
       </c>
       <c r="AD5" t="n">
         <v>1.3</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>7.15</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46024.53125</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>7.9</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>7.15</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>4.95</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46024.53125</v>
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="M12" t="n">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="N12" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="O12" t="n">
         <v>6.69</v>
@@ -1897,7 +1897,7 @@
         <v>1.95</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AC12" t="n">
         <v>3.24</v>
@@ -1968,16 +1968,16 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="M13" t="n">
-        <v>3.5</v>
+        <v>3.62</v>
       </c>
       <c r="N13" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="O13" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="P13" t="n">
         <v>2.1</v>
@@ -1986,16 +1986,16 @@
         <v>5.25</v>
       </c>
       <c r="R13" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="S13" t="n">
-        <v>2.7</v>
+        <v>2.53</v>
       </c>
       <c r="T13" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="U13" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="V13" t="n">
         <v>7.5</v>
@@ -2010,13 +2010,13 @@
         <v>1.34</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AC13" t="n">
         <v>3.62</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.8</v>
+        <v>5.5</v>
       </c>
       <c r="M14" t="n">
-        <v>3.35</v>
+        <v>3.99</v>
       </c>
       <c r="N14" t="n">
-        <v>2.6</v>
+        <v>1.57</v>
       </c>
       <c r="O14" t="n">
-        <v>3</v>
+        <v>5.9</v>
       </c>
       <c r="P14" t="n">
-        <v>2.09</v>
+        <v>2.25</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.1</v>
+        <v>2.12</v>
       </c>
       <c r="R14" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="S14" t="n">
-        <v>2.85</v>
+        <v>2.91</v>
       </c>
       <c r="T14" t="n">
-        <v>2.75</v>
+        <v>2.83</v>
       </c>
       <c r="U14" t="n">
         <v>1.42</v>
       </c>
       <c r="V14" t="n">
-        <v>6.5</v>
+        <v>6.75</v>
       </c>
       <c r="W14" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X14" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="Z14" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AC14" t="n">
         <v>3.4</v>
       </c>
-      <c r="AA14" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>3.3</v>
-      </c>
       <c r="AD14" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.67</v>
+        <v>1.94</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.1</v>
+        <v>1.79</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.4</v>
+        <v>1.15</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46024.69791666666</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.65</v>
+        <v>2.8</v>
       </c>
       <c r="M15" t="n">
-        <v>3.05</v>
+        <v>3.35</v>
       </c>
       <c r="N15" t="n">
-        <v>2.48</v>
+        <v>2.6</v>
       </c>
       <c r="O15" t="n">
-        <v>3.44</v>
+        <v>3</v>
       </c>
       <c r="P15" t="n">
-        <v>2.04</v>
+        <v>2.09</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.16</v>
+        <v>3.1</v>
       </c>
       <c r="R15" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="S15" t="n">
-        <v>2.47</v>
+        <v>2.85</v>
       </c>
       <c r="T15" t="n">
-        <v>3.08</v>
+        <v>2.75</v>
       </c>
       <c r="U15" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V15" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AD15" t="n">
         <v>1.3</v>
       </c>
-      <c r="V15" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.18</v>
-      </c>
       <c r="AE15" t="n">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.84</v>
+        <v>2.1</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46024.69791666666</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>5.5</v>
+        <v>2.4</v>
       </c>
       <c r="M16" t="n">
-        <v>4</v>
+        <v>3.1</v>
       </c>
       <c r="N16" t="n">
-        <v>1.55</v>
+        <v>2.8</v>
       </c>
       <c r="O16" t="n">
-        <v>6</v>
+        <v>3.44</v>
       </c>
       <c r="P16" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V16" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AA16" t="n">
         <v>2.25</v>
       </c>
-      <c r="Q16" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="V16" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>3.71</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AB16" t="n">
-        <v>1.92</v>
+        <v>1.58</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.4</v>
+        <v>3.82</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.78</v>
+        <v>1.84</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.15</v>
+        <v>1.37</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46024.69791666666</v>
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.93</v>
+        <v>2.02</v>
       </c>
       <c r="M18" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="N18" t="n">
-        <v>4.12</v>
+        <v>3.7</v>
       </c>
       <c r="O18" t="n">
         <v>2.5</v>
@@ -2608,10 +2608,10 @@
         <v>2.89</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.76</v>
+        <v>1.6</v>
       </c>
       <c r="AC18" t="n">
         <v>4</v>

--- a/jogos_2026-01-02.xlsx
+++ b/jogos_2026-01-02.xlsx
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>5.5</v>
+        <v>2.4</v>
       </c>
       <c r="M14" t="n">
-        <v>3.99</v>
+        <v>3.1</v>
       </c>
       <c r="N14" t="n">
-        <v>1.57</v>
+        <v>2.8</v>
       </c>
       <c r="O14" t="n">
-        <v>5.9</v>
+        <v>3.44</v>
       </c>
       <c r="P14" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V14" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AA14" t="n">
         <v>2.25</v>
       </c>
-      <c r="Q14" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="V14" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.92</v>
-      </c>
       <c r="AB14" t="n">
-        <v>1.82</v>
+        <v>1.58</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.4</v>
+        <v>3.82</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.31</v>
+        <v>1.18</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.79</v>
+        <v>1.84</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.15</v>
+        <v>1.37</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46024.69791666666</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.4</v>
+        <v>5.5</v>
       </c>
       <c r="M16" t="n">
-        <v>3.1</v>
+        <v>3.99</v>
       </c>
       <c r="N16" t="n">
-        <v>2.8</v>
+        <v>1.57</v>
       </c>
       <c r="O16" t="n">
-        <v>3.44</v>
+        <v>5.9</v>
       </c>
       <c r="P16" t="n">
-        <v>2.04</v>
+        <v>2.25</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.16</v>
+        <v>2.12</v>
       </c>
       <c r="R16" t="n">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="S16" t="n">
-        <v>2.47</v>
+        <v>2.91</v>
       </c>
       <c r="T16" t="n">
-        <v>3.08</v>
+        <v>2.83</v>
       </c>
       <c r="U16" t="n">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="V16" t="n">
-        <v>8.1</v>
+        <v>6.75</v>
       </c>
       <c r="W16" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.38</v>
+        <v>1.27</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.74</v>
+        <v>3.36</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.25</v>
+        <v>1.92</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.58</v>
+        <v>1.82</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.82</v>
+        <v>3.4</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.18</v>
+        <v>1.31</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.84</v>
+        <v>1.79</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.37</v>
+        <v>1.15</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46024.69791666666</v>

--- a/jogos_2026-01-02.xlsx
+++ b/jogos_2026-01-02.xlsx
@@ -674,13 +674,13 @@
         <v>2.44</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.59</v>
+        <v>4.6</v>
       </c>
       <c r="R2" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S2" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="T2" t="n">
         <v>2.4</v>
@@ -695,7 +695,7 @@
         <v>1.08</v>
       </c>
       <c r="X2" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y2" t="n">
         <v>1.18</v>
@@ -722,10 +722,10 @@
         <v>2.13</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46024.23263888889</v>
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="M4" t="n">
-        <v>3.9</v>
+        <v>4.15</v>
       </c>
       <c r="N4" t="n">
-        <v>4.61</v>
+        <v>4.6</v>
       </c>
       <c r="O4" t="n">
         <v>2.13</v>
@@ -942,13 +942,13 @@
         <v>4.55</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AB4" t="n">
         <v>2.25</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="AD4" t="n">
         <v>1.46</v>
@@ -1058,16 +1058,16 @@
         <v>1.24</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.34</v>
+        <v>3.55</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AB5" t="n">
         <v>1.85</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.05</v>
+        <v>2.97</v>
       </c>
       <c r="AD5" t="n">
         <v>1.3</v>
@@ -1153,10 +1153,10 @@
         <v>2.41</v>
       </c>
       <c r="R6" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="S6" t="n">
-        <v>3.02</v>
+        <v>3.08</v>
       </c>
       <c r="T6" t="n">
         <v>2.47</v>
@@ -1165,16 +1165,16 @@
         <v>1.45</v>
       </c>
       <c r="V6" t="n">
-        <v>6</v>
+        <v>5.95</v>
       </c>
       <c r="W6" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X6" t="n">
         <v>1.03</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="Z6" t="n">
         <v>4.05</v>
@@ -1183,19 +1183,19 @@
         <v>1.67</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.66</v>
+        <v>2.59</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AE6" t="n">
         <v>1.59</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.19</v>
+        <v>2.23</v>
       </c>
       <c r="AG6" t="n">
         <v>1.22</v>
@@ -1299,10 +1299,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1373,28 +1373,28 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.29</v>
+        <v>1.45</v>
       </c>
       <c r="M8" t="n">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="N8" t="n">
-        <v>7.9</v>
+        <v>5.9</v>
       </c>
       <c r="O8" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="P8" t="n">
-        <v>2.44</v>
+        <v>2.41</v>
       </c>
       <c r="Q8" t="n">
-        <v>7.15</v>
+        <v>7.21</v>
       </c>
       <c r="R8" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S8" t="n">
-        <v>3.25</v>
+        <v>3.18</v>
       </c>
       <c r="T8" t="n">
         <v>2.27</v>
@@ -1409,7 +1409,7 @@
         <v>1.11</v>
       </c>
       <c r="X8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y8" t="n">
         <v>1.14</v>
@@ -1421,13 +1421,13 @@
         <v>1.57</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AE8" t="n">
         <v>1.82</v>
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.13</v>
+        <v>3.7</v>
       </c>
       <c r="M11" t="n">
-        <v>3.42</v>
+        <v>3.85</v>
       </c>
       <c r="N11" t="n">
-        <v>2.05</v>
+        <v>1.75</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1858,7 +1858,7 @@
         <v>1.52</v>
       </c>
       <c r="O12" t="n">
-        <v>6.69</v>
+        <v>6.96</v>
       </c>
       <c r="P12" t="n">
         <v>2.17</v>
@@ -1867,7 +1867,7 @@
         <v>2.08</v>
       </c>
       <c r="R12" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="S12" t="n">
         <v>2.73</v>
@@ -1888,7 +1888,7 @@
         <v>1.06</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="Z12" t="n">
         <v>3.12</v>
@@ -1912,7 +1912,7 @@
         <v>1.71</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.26</v>
+        <v>2.41</v>
       </c>
       <c r="AH12" t="n">
         <v>1.13</v>
@@ -1977,7 +1977,7 @@
         <v>5.9</v>
       </c>
       <c r="O13" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="P13" t="n">
         <v>2.1</v>
@@ -1986,7 +1986,7 @@
         <v>5.25</v>
       </c>
       <c r="R13" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="S13" t="n">
         <v>2.53</v>
@@ -2034,7 +2034,7 @@
         <v>1.28</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46024.6875</v>
@@ -2096,19 +2096,19 @@
         <v>2.8</v>
       </c>
       <c r="O14" t="n">
-        <v>3.44</v>
+        <v>3.06</v>
       </c>
       <c r="P14" t="n">
         <v>2.04</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.16</v>
+        <v>3.79</v>
       </c>
       <c r="R14" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="S14" t="n">
-        <v>2.47</v>
+        <v>2.44</v>
       </c>
       <c r="T14" t="n">
         <v>3.08</v>
@@ -2117,13 +2117,13 @@
         <v>1.3</v>
       </c>
       <c r="V14" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="W14" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X14" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="Y14" t="n">
         <v>1.38</v>
@@ -2138,22 +2138,22 @@
         <v>1.58</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.82</v>
+        <v>3.74</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AE14" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AF14" t="n">
         <v>1.85</v>
       </c>
-      <c r="AF14" t="n">
-        <v>1.84</v>
-      </c>
       <c r="AG14" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.37</v>
+        <v>1.47</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46024.69791666666</v>
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="M15" t="n">
-        <v>3.35</v>
+        <v>3.33</v>
       </c>
       <c r="N15" t="n">
-        <v>2.6</v>
+        <v>2.46</v>
       </c>
       <c r="O15" t="n">
         <v>3</v>
@@ -2221,7 +2221,7 @@
         <v>2.09</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="R15" t="n">
         <v>1.42</v>
@@ -2230,16 +2230,16 @@
         <v>2.85</v>
       </c>
       <c r="T15" t="n">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="U15" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="V15" t="n">
-        <v>6.5</v>
+        <v>7.6</v>
       </c>
       <c r="W15" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X15" t="n">
         <v>1.02</v>
@@ -2251,10 +2251,10 @@
         <v>3.4</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.99</v>
+        <v>1.85</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.8</v>
+        <v>1.89</v>
       </c>
       <c r="AC15" t="n">
         <v>3.3</v>
@@ -2263,13 +2263,13 @@
         <v>1.3</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AH15" t="n">
         <v>1.4</v>
@@ -2346,7 +2346,7 @@
         <v>1.38</v>
       </c>
       <c r="S16" t="n">
-        <v>2.91</v>
+        <v>3.06</v>
       </c>
       <c r="T16" t="n">
         <v>2.83</v>
@@ -2364,7 +2364,7 @@
         <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="Z16" t="n">
         <v>3.36</v>
@@ -2382,16 +2382,16 @@
         <v>1.31</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46024.69791666666</v>
@@ -2444,28 +2444,28 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.22</v>
+        <v>2.19</v>
       </c>
       <c r="M17" t="n">
-        <v>3.05</v>
+        <v>2.95</v>
       </c>
       <c r="N17" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="O17" t="n">
-        <v>2.96</v>
+        <v>2.75</v>
       </c>
       <c r="P17" t="n">
         <v>1.91</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.75</v>
+        <v>4.54</v>
       </c>
       <c r="R17" t="n">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="S17" t="n">
-        <v>2.31</v>
+        <v>2.16</v>
       </c>
       <c r="T17" t="n">
         <v>4.2</v>
@@ -2492,7 +2492,7 @@
         <v>2.93</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AC17" t="n">
         <v>5.8</v>
@@ -2501,13 +2501,13 @@
         <v>1.07</v>
       </c>
       <c r="AE17" t="n">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AH17" t="n">
         <v>1.65</v>

--- a/jogos_2026-01-02.xlsx
+++ b/jogos_2026-01-02.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI18"/>
+  <dimension ref="A1:AI19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>4.93</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46024.41319444445</v>
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.93</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46024.41319444445</v>
@@ -1570,12 +1570,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,10 +1656,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1680,7 +1680,7 @@
         <v>0</v>
       </c>
       <c r="AI10" s="3" t="n">
-        <v>46024.58333333334</v>
+        <v>46024.54166666666</v>
       </c>
     </row>
     <row r="11">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.7</v>
+        <v>2.13</v>
       </c>
       <c r="M11" t="n">
-        <v>3.85</v>
+        <v>3.25</v>
       </c>
       <c r="N11" t="n">
-        <v>1.75</v>
+        <v>3.4</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.53</v>
+        <v>2.1</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.37</v>
+        <v>1.65</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1799,7 +1799,7 @@
         <v>0</v>
       </c>
       <c r="AI11" s="3" t="n">
-        <v>46024.60416666666</v>
+        <v>46024.58333333334</v>
       </c>
     </row>
     <row r="12">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,76 +1849,76 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>6.3</v>
+        <v>3.7</v>
       </c>
       <c r="M12" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="N12" t="n">
-        <v>1.52</v>
+        <v>1.75</v>
       </c>
       <c r="O12" t="n">
-        <v>6.96</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.95</v>
+        <v>1.53</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.75</v>
+        <v>2.37</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AI12" s="3" t="n">
-        <v>46024.65625</v>
+        <v>46024.60416666666</v>
       </c>
     </row>
     <row r="13">
@@ -1927,12 +1927,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,76 +1968,76 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.6</v>
+        <v>6.3</v>
       </c>
       <c r="M13" t="n">
-        <v>3.62</v>
+        <v>3.95</v>
       </c>
       <c r="N13" t="n">
-        <v>5.9</v>
+        <v>1.52</v>
       </c>
       <c r="O13" t="n">
-        <v>2.18</v>
+        <v>6.96</v>
       </c>
       <c r="P13" t="n">
-        <v>2.1</v>
+        <v>2.17</v>
       </c>
       <c r="Q13" t="n">
-        <v>5.25</v>
+        <v>2.08</v>
       </c>
       <c r="R13" t="n">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="S13" t="n">
-        <v>2.53</v>
+        <v>2.73</v>
       </c>
       <c r="T13" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="U13" t="n">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="V13" t="n">
-        <v>7.5</v>
+        <v>6.75</v>
       </c>
       <c r="W13" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X13" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.8</v>
+        <v>3.12</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.62</v>
+        <v>3.24</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.11</v>
+        <v>2.02</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.28</v>
+        <v>2.41</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.27</v>
+        <v>1.13</v>
       </c>
       <c r="AI13" s="3" t="n">
-        <v>46024.6875</v>
+        <v>46024.65625</v>
       </c>
     </row>
     <row r="14">
@@ -2046,12 +2046,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,76 +2087,76 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
       <c r="M14" t="n">
-        <v>3.1</v>
+        <v>3.62</v>
       </c>
       <c r="N14" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="O14" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="V14" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="Z14" t="n">
         <v>2.8</v>
       </c>
-      <c r="O14" t="n">
-        <v>3.06</v>
-      </c>
-      <c r="P14" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>3.79</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="T14" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V14" t="n">
-        <v>8</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>2.74</v>
-      </c>
       <c r="AA14" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.74</v>
+        <v>3.62</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.84</v>
+        <v>2.11</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.47</v>
+        <v>2.27</v>
       </c>
       <c r="AI14" s="3" t="n">
-        <v>46024.69791666666</v>
+        <v>46024.6875</v>
       </c>
     </row>
     <row r="15">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.76</v>
+        <v>2.4</v>
       </c>
       <c r="M15" t="n">
-        <v>3.33</v>
+        <v>3.1</v>
       </c>
       <c r="N15" t="n">
-        <v>2.46</v>
+        <v>2.8</v>
       </c>
       <c r="O15" t="n">
-        <v>3</v>
+        <v>3.06</v>
       </c>
       <c r="P15" t="n">
-        <v>2.09</v>
+        <v>2.04</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.15</v>
+        <v>3.79</v>
       </c>
       <c r="R15" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="S15" t="n">
-        <v>2.85</v>
+        <v>2.44</v>
       </c>
       <c r="T15" t="n">
-        <v>2.9</v>
+        <v>3.08</v>
       </c>
       <c r="U15" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="V15" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="W15" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X15" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.4</v>
+        <v>2.74</v>
       </c>
       <c r="AA15" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AF15" t="n">
         <v>1.85</v>
       </c>
-      <c r="AB15" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AD15" t="n">
+      <c r="AG15" t="n">
         <v>1.3</v>
       </c>
-      <c r="AE15" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AH15" t="n">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46024.69791666666</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>5.5</v>
+        <v>2.76</v>
       </c>
       <c r="M16" t="n">
-        <v>3.99</v>
+        <v>3.33</v>
       </c>
       <c r="N16" t="n">
-        <v>1.57</v>
+        <v>2.46</v>
       </c>
       <c r="O16" t="n">
-        <v>5.9</v>
+        <v>3</v>
       </c>
       <c r="P16" t="n">
-        <v>2.25</v>
+        <v>2.09</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.12</v>
+        <v>3.15</v>
       </c>
       <c r="R16" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="S16" t="n">
-        <v>3.06</v>
+        <v>2.85</v>
       </c>
       <c r="T16" t="n">
-        <v>2.83</v>
+        <v>2.9</v>
       </c>
       <c r="U16" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="V16" t="n">
-        <v>6.75</v>
+        <v>7.6</v>
       </c>
       <c r="W16" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X16" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y16" t="n">
         <v>1.29</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.36</v>
+        <v>3.4</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.82</v>
+        <v>1.89</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.91</v>
+        <v>1.7</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.82</v>
+        <v>2.05</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.12</v>
+        <v>1.4</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46024.69791666666</v>
@@ -2403,12 +2403,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,76 +2444,76 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.19</v>
+        <v>5.5</v>
       </c>
       <c r="M17" t="n">
-        <v>2.95</v>
+        <v>3.99</v>
       </c>
       <c r="N17" t="n">
-        <v>3.95</v>
+        <v>1.57</v>
       </c>
       <c r="O17" t="n">
-        <v>2.75</v>
+        <v>5.9</v>
       </c>
       <c r="P17" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V17" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AE17" t="n">
         <v>1.91</v>
       </c>
-      <c r="Q17" t="n">
-        <v>4.54</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="T17" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="V17" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1</v>
-      </c>
-      <c r="X17" t="n">
+      <c r="AF17" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AH17" t="n">
         <v>1.12</v>
       </c>
-      <c r="Y17" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1.65</v>
-      </c>
       <c r="AI17" s="3" t="n">
-        <v>46024.70833333334</v>
+        <v>46024.69791666666</v>
       </c>
     </row>
     <row r="18">
@@ -2522,116 +2522,235 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Spain La Liga</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Rayo Vallecano</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Getafe CF</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="M18" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="N18" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="O18" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>4.54</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="T18" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="V18" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AI18" s="3" t="n">
+        <v>46024.70833333334</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>46024</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
           <t>17:45</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>Portugal Liga NOS</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>Vitória Guimarães</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>CD Nacional</t>
         </is>
       </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="inlineStr">
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L18" t="n">
+      <c r="L19" t="n">
         <v>2.02</v>
       </c>
-      <c r="M18" t="n">
+      <c r="M19" t="n">
         <v>3.3</v>
       </c>
-      <c r="N18" t="n">
+      <c r="N19" t="n">
         <v>3.7</v>
       </c>
-      <c r="O18" t="n">
+      <c r="O19" t="n">
         <v>2.5</v>
       </c>
-      <c r="P18" t="n">
+      <c r="P19" t="n">
         <v>2.08</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="Q19" t="n">
         <v>4.7</v>
       </c>
-      <c r="R18" t="n">
+      <c r="R19" t="n">
         <v>1.42</v>
       </c>
-      <c r="S18" t="n">
+      <c r="S19" t="n">
         <v>2.59</v>
       </c>
-      <c r="T18" t="n">
+      <c r="T19" t="n">
         <v>3.02</v>
       </c>
-      <c r="U18" t="n">
+      <c r="U19" t="n">
         <v>1.36</v>
       </c>
-      <c r="V18" t="n">
+      <c r="V19" t="n">
         <v>7</v>
       </c>
-      <c r="W18" t="n">
+      <c r="W19" t="n">
         <v>1.07</v>
       </c>
-      <c r="X18" t="n">
+      <c r="X19" t="n">
         <v>1.03</v>
       </c>
-      <c r="Y18" t="n">
+      <c r="Y19" t="n">
         <v>1.32</v>
       </c>
-      <c r="Z18" t="n">
+      <c r="Z19" t="n">
         <v>2.89</v>
       </c>
-      <c r="AA18" t="n">
+      <c r="AA19" t="n">
         <v>2.2</v>
       </c>
-      <c r="AB18" t="n">
+      <c r="AB19" t="n">
         <v>1.6</v>
       </c>
-      <c r="AC18" t="n">
+      <c r="AC19" t="n">
         <v>4</v>
       </c>
-      <c r="AD18" t="n">
+      <c r="AD19" t="n">
         <v>1.22</v>
       </c>
-      <c r="AE18" t="n">
+      <c r="AE19" t="n">
         <v>1.88</v>
       </c>
-      <c r="AF18" t="n">
+      <c r="AF19" t="n">
         <v>1.82</v>
       </c>
-      <c r="AG18" t="n">
+      <c r="AG19" t="n">
         <v>1.34</v>
       </c>
-      <c r="AH18" t="n">
+      <c r="AH19" t="n">
         <v>1.89</v>
       </c>
-      <c r="AI18" s="3" t="n">
+      <c r="AI19" s="3" t="n">
         <v>46024.73958333334</v>
       </c>
     </row>

--- a/jogos_2026-01-02.xlsx
+++ b/jogos_2026-01-02.xlsx
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="M2" t="n">
-        <v>3.85</v>
+        <v>3.84</v>
       </c>
       <c r="N2" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="O2" t="n">
         <v>2.3</v>
@@ -707,7 +707,7 @@
         <v>1.65</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AC2" t="n">
         <v>2.64</v>
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.93</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46024.41319444445</v>
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>4.93</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46024.41319444445</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>7.21</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>4.95</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46024.53125</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>7.21</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46024.53125</v>
